--- a/output/pdf_financials_xlsx/USS.xlsx
+++ b/output/pdf_financials_xlsx/USS.xlsx
@@ -2414,13 +2414,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.196651</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.088521</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.415681</v>
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
@@ -2428,34 +2428,34 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.061217</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.09921099999999999</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.137844</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.049315</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.867753</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.290785</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.249771</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.673768</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.411573</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>1.957346</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>1.758638</v>
@@ -2534,13 +2534,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.196651</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.088521</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.415681</v>
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
@@ -2548,34 +2548,34 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.061217</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.09921099999999999</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.137844</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.049315</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.867753</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.290785</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.249771</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.673768</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.411573</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>1.957346</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>1.758638</v>
@@ -3254,13 +3254,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.976277</v>
+        <v>2.779626</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.297432</v>
+        <v>0.208911</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.46842</v>
+        <v>0.052739</v>
       </c>
       <c r="E48" s="1" t="inlineStr">
         <is>
@@ -3268,34 +3268,34 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.1719</v>
+        <v>0.110683</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.157936</v>
+        <v>0.058725</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.23201</v>
+        <v>0.094166</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.22292</v>
+        <v>0.173605</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.052243</v>
+        <v>0.18449</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.764072</v>
+        <v>0.473287</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.350856</v>
+        <v>0.101085</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.820612</v>
+        <v>0.146844</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.560967</v>
+        <v>0.149394</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>2.146272</v>
+        <v>0.188926</v>
       </c>
       <c r="P48" s="3" t="n">
         <v>0.301679</v>
@@ -13715,7 +13715,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -16190,7 +16190,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E79" s="5" t="n">
@@ -18501,7 +18501,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -24251,7 +24251,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -26923,7 +26923,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">

--- a/output/pdf_financials_xlsx/USS.xlsx
+++ b/output/pdf_financials_xlsx/USS.xlsx
@@ -6391,22 +6391,22 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.554725</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.299702</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.012472</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.018328</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.008404</v>
       </c>
       <c r="H100" s="3" t="n">
         <v>0</v>
@@ -6418,28 +6418,28 @@
         <v>0</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.040527</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.174068</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.137351</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.072202</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.055863</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>0.046059</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>0.025991</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>0.079058</v>
       </c>
     </row>
     <row r="101">
@@ -7093,13 +7093,13 @@
         <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.030323</v>
       </c>
       <c r="E112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.00152</v>
       </c>
       <c r="G112" s="3" t="n">
         <v>0</v>
@@ -7111,7 +7111,7 @@
         <v>0</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.008501</v>
       </c>
       <c r="K112" s="3" t="n">
         <v>0</v>
@@ -7560,10 +7560,10 @@
         <v>0</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>0</v>
+        <v>0.528164</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>0</v>
+        <v>0.215865</v>
       </c>
       <c r="G120" s="3" t="n">
         <v>0</v>
@@ -33326,7 +33326,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -43438,7 +43438,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -44030,7 +44030,11 @@
           <t>Proceeds on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr"/>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
           <t>-</t>
@@ -48685,7 +48689,11 @@
           <t>Proceeds on disposal of Property and Equipment</t>
         </is>
       </c>
-      <c r="D404" t="inlineStr"/>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E404" t="inlineStr">
         <is>
           <t>-</t>
@@ -56618,7 +56626,11 @@
           <t>Loss on disposal of Property and Equipment</t>
         </is>
       </c>
-      <c r="D483" t="inlineStr"/>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E483" t="inlineStr">
         <is>
           <t>-</t>
@@ -59432,7 +59444,7 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E511" s="5" t="n">
@@ -60325,7 +60337,11 @@
           <t>Issuance of common shares, net of issuance costs</t>
         </is>
       </c>
-      <c r="D520" t="inlineStr"/>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E520" t="inlineStr">
         <is>
           <t>-</t>
@@ -64735,7 +64751,11 @@
           <t>Proceeds on sale of property and equipment</t>
         </is>
       </c>
-      <c r="D564" t="inlineStr"/>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E564" t="inlineStr">
         <is>
           <t>-</t>
@@ -70373,7 +70393,11 @@
           <t>Amortization of intangible assets 8b</t>
         </is>
       </c>
-      <c r="D620" t="inlineStr"/>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E620" t="inlineStr">
         <is>
           <t>-</t>
@@ -71842,7 +71866,11 @@
           <t>Amortization of intangible assets 7b</t>
         </is>
       </c>
-      <c r="D635" t="inlineStr"/>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E635" t="inlineStr">
         <is>
           <t>-</t>
@@ -76192,7 +76220,11 @@
           <t>Amortization of intangible assets 6c</t>
         </is>
       </c>
-      <c r="D679" t="inlineStr"/>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E679" t="inlineStr">
         <is>
           <t>-</t>
@@ -79360,7 +79392,7 @@
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
@@ -81572,7 +81604,7 @@
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">
@@ -83986,7 +84018,7 @@
       </c>
       <c r="D757" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E757" t="inlineStr">
@@ -87087,7 +87119,7 @@
       </c>
       <c r="D788" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E788" s="5" t="n">

--- a/output/pdf_financials_xlsx/USS.xlsx
+++ b/output/pdf_financials_xlsx/USS.xlsx
@@ -1370,7 +1370,7 @@
         <v>-0</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.25725</v>
+        <v>-0.25725</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>-0</v>
@@ -1608,8 +1608,10 @@
       <c r="E20" s="3" t="n">
         <v>-2.786713</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>-1.485282</v>
+      <c r="F20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G20" s="3" t="n">
         <v>0.134483</v>
@@ -1667,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0</v>
+        <v>-0.583008</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>0</v>
@@ -4621,10 +4623,10 @@
         <v>0</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>0.070062</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>0.297972</v>
       </c>
       <c r="E70" s="1" t="inlineStr">
         <is>
@@ -4632,7 +4634,7 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0</v>
+        <v>0.366085</v>
       </c>
       <c r="G70" s="3" t="n">
         <v>0</v>
@@ -4681,10 +4683,10 @@
         <v>0</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0</v>
+        <v>0.070062</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0</v>
+        <v>0.297972</v>
       </c>
       <c r="E71" s="1" t="inlineStr">
         <is>
@@ -4692,7 +4694,7 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.39</v>
+        <v>0.756085</v>
       </c>
       <c r="G71" s="3" t="n">
         <v>0.012335</v>
@@ -4921,10 +4923,10 @@
         <v>0.16659</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>2.110763</v>
+        <v>2.040701</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>5.422353</v>
+        <v>5.124381</v>
       </c>
       <c r="E75" s="1" t="inlineStr">
         <is>
@@ -4932,7 +4934,7 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>5.609463</v>
+        <v>5.243378</v>
       </c>
       <c r="G75" s="3" t="n">
         <v>2.592879</v>
@@ -5222,15 +5224,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C80" s="3" t="n">
+        <v>0.03782101873074859</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>-0.0705176887051996</v>
       </c>
       <c r="E80" s="1" t="inlineStr">
         <is>
@@ -5238,7 +5236,7 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>-0.06002930353540274</v>
+        <v>-0.1163775793937564</v>
       </c>
       <c r="G80" s="3" t="n">
         <v>-0.002241638244111225</v>
@@ -6348,7 +6346,7 @@
         <v>-1.485282</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>-0.401542</v>
+        <v>0.134483</v>
       </c>
       <c r="H99" s="3" t="n">
         <v>-0.401542</v>
@@ -6357,7 +6355,7 @@
         <v>-0.957725</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>-0.957725</v>
+        <v>0.07134799999999999</v>
       </c>
       <c r="K99" s="3" t="n">
         <v>-4.016861</v>
@@ -6739,16 +6737,16 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0</v>
+        <v>0.98363</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-1.318442</v>
+        <v>-2.04768</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.414685</v>
+        <v>0.9043909999999999</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>-0.101775</v>
+        <v>0.315408</v>
       </c>
       <c r="F106" s="3" t="n">
         <v>0</v>
@@ -7288,7 +7286,7 @@
         <v>0</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.400026</v>
       </c>
       <c r="L115" s="3" t="n">
         <v>0</v>
@@ -8194,30 +8192,20 @@
       <c r="K130" s="3" t="n">
         <v>0.867753</v>
       </c>
-      <c r="L130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L130" s="3" t="n">
+        <v>0.290785</v>
+      </c>
+      <c r="M130" s="3" t="n">
+        <v>0.249771</v>
+      </c>
+      <c r="N130" s="3" t="n">
+        <v>0.673768</v>
+      </c>
+      <c r="O130" s="3" t="n">
+        <v>0.411573</v>
+      </c>
+      <c r="P130" s="3" t="n">
+        <v>1.957346</v>
       </c>
       <c r="Q130" s="3" t="n">
         <v>1.758638</v>
@@ -8378,30 +8366,20 @@
       <c r="K133" s="3" t="n">
         <v>0.290785</v>
       </c>
-      <c r="L133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L133" s="3" t="n">
+        <v>0.249771</v>
+      </c>
+      <c r="M133" s="3" t="n">
+        <v>0.673768</v>
+      </c>
+      <c r="N133" s="3" t="n">
+        <v>0.411573</v>
+      </c>
+      <c r="O133" s="3" t="n">
+        <v>1.957346</v>
+      </c>
+      <c r="P133" s="3" t="n">
+        <v>1.758638</v>
       </c>
       <c r="Q133" s="3" t="n">
         <v>1.11147</v>
@@ -8537,7 +8515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U808"/>
+  <dimension ref="A1:U833"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -15081,7 +15059,11 @@
           <t>Intangible assets and goodwill 7b</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>GoodwillAndOtherIntangibleAssets</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -25501,7 +25483,11 @@
           <t>Current portion of finance lease obligations (Note 12) 218,805</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>
@@ -28141,7 +28127,11 @@
           <t>Current portion of finance lease obligations (note 15) 366,085</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
@@ -38022,7 +38012,11 @@
           <t>Cash at beginning of the year</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr"/>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr">
         <is>
           <t>-</t>
@@ -38115,7 +38109,11 @@
           <t>Cash at end of the year $</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr"/>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E298" t="inlineStr">
         <is>
           <t>-</t>
@@ -43337,7 +43335,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D350" t="inlineStr"/>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E350" t="inlineStr">
         <is>
           <t>-</t>
@@ -44135,7 +44137,11 @@
           <t>Proceeds on sales of investment</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr"/>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E358" t="inlineStr">
         <is>
           <t>-</t>
@@ -47626,7 +47632,11 @@
           <t>Net Income (Loss)</t>
         </is>
       </c>
-      <c r="D393" t="inlineStr"/>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E393" t="inlineStr">
         <is>
           <t>-</t>
@@ -54218,7 +54228,11 @@
           <t>Deferred Income Tax Recovery</t>
         </is>
       </c>
-      <c r="D459" t="inlineStr"/>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E459" t="inlineStr">
         <is>
           <t>-</t>
@@ -55523,7 +55537,11 @@
           <t>Deferred Income Tax Recovery - - -</t>
         </is>
       </c>
-      <c r="D472" t="inlineStr"/>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E472" t="inlineStr">
         <is>
           <t>-</t>
@@ -58848,7 +58866,11 @@
           <t>Deferred Income Tax Recovery 18 -</t>
         </is>
       </c>
-      <c r="D505" t="inlineStr"/>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E505" t="inlineStr">
         <is>
           <t>-</t>
@@ -61652,7 +61674,11 @@
           <t>Changes in non‐cash operating working capital (note 21(a))</t>
         </is>
       </c>
-      <c r="D533" t="inlineStr"/>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E533" t="inlineStr">
         <is>
           <t>-</t>
@@ -64054,7 +64080,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D557" t="inlineStr"/>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E557" s="5" t="n">
         <v>-0.064341</v>
       </c>
@@ -64151,7 +64181,11 @@
           <t>Changes in non-cash operating working capital (Note 20(a))</t>
         </is>
       </c>
-      <c r="D558" t="inlineStr"/>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E558" t="inlineStr">
         <is>
           <t>-</t>
@@ -68084,7 +68118,11 @@
           <t>Changes in non-cash operating working capital (Note 19(a))</t>
         </is>
       </c>
-      <c r="D597" t="inlineStr"/>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E597" s="5" t="n">
         <v>0.98363</v>
       </c>
@@ -79796,7 +79834,11 @@
           <t>Deferred Income Tax Recovery 17</t>
         </is>
       </c>
-      <c r="D715" t="inlineStr"/>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E715" t="inlineStr">
         <is>
           <t>-</t>
@@ -80895,7 +80937,11 @@
           <t>Deferred income tax recovery 18</t>
         </is>
       </c>
-      <c r="D726" t="inlineStr"/>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E726" t="inlineStr">
         <is>
           <t>-</t>
@@ -81091,12 +81137,12 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>Note 5 and 23</t>
+          <t>31 May</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>Revenues</t>
+          <t>Revenue 6,765,786</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
@@ -81114,16 +81160,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G728" s="5" t="n">
-        <v>8.161194</v>
-      </c>
-      <c r="H728" s="5" t="n">
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H728" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I728" s="5" t="n">
         <v>7.372128</v>
-      </c>
-      <c r="I728" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="J728" t="inlineStr">
         <is>
@@ -81194,12 +81242,12 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>Note 5 and 23</t>
+          <t>31 May</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>Cost of revenues</t>
+          <t>Cost of revenues 3,389,759</t>
         </is>
       </c>
       <c r="D729" t="inlineStr">
@@ -81217,16 +81265,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G729" s="5" t="n">
-        <v>4.266365</v>
-      </c>
-      <c r="H729" s="5" t="n">
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H729" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I729" s="5" t="n">
         <v>3.741237</v>
-      </c>
-      <c r="I729" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="J729" t="inlineStr">
         <is>
@@ -81297,12 +81347,12 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>Note 5 and 23</t>
+          <t>31 May</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>Note 5 and 23 total</t>
+          <t>31 May total</t>
         </is>
       </c>
       <c r="D730" t="inlineStr"/>
@@ -81316,16 +81366,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G730" s="5" t="n">
-        <v>3.894829</v>
-      </c>
-      <c r="H730" s="5" t="n">
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I730" s="5" t="n">
         <v>3.630891</v>
-      </c>
-      <c r="I730" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="J730" t="inlineStr">
         <is>
@@ -81401,7 +81453,7 @@
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>Operations and administration expenses</t>
+          <t>Operations and administration (Notes 8 and 17) 2,839,495</t>
         </is>
       </c>
       <c r="D731" t="inlineStr"/>
@@ -81415,16 +81467,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G731" s="5" t="n">
-        <v>4.531915</v>
-      </c>
-      <c r="H731" s="5" t="n">
-        <v>3.555414</v>
-      </c>
-      <c r="I731" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I731" s="5" t="n">
+        <v>3.702791</v>
       </c>
       <c r="J731" t="inlineStr">
         <is>
@@ -81500,7 +81554,7 @@
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>Amortization of property and equipment (note 7)</t>
+          <t>Amortization of property and equipment (Note 6) 357,183</t>
         </is>
       </c>
       <c r="D732" t="inlineStr"/>
@@ -81514,16 +81568,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G732" s="5" t="n">
-        <v>0.354236</v>
-      </c>
-      <c r="H732" s="5" t="n">
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H732" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I732" s="5" t="n">
         <v>0.358557</v>
-      </c>
-      <c r="I732" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="J732" t="inlineStr">
         <is>
@@ -81599,7 +81655,7 @@
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>Amortization of intangible assets (note 8)</t>
+          <t>Amortization of intangible assets (Note 7) 18,328</t>
         </is>
       </c>
       <c r="D733" t="inlineStr">
@@ -81617,16 +81673,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G733" s="5" t="n">
-        <v>0.299702</v>
-      </c>
-      <c r="H733" s="5" t="n">
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I733" s="5" t="n">
         <v>0.012472</v>
-      </c>
-      <c r="I733" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="J733" t="inlineStr">
         <is>
@@ -81702,7 +81760,7 @@
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>Amortization of deferred finance costs (note 8)</t>
+          <t>Amortization of deferred finance costs (Note 7) 16,234</t>
         </is>
       </c>
       <c r="D734" t="inlineStr"/>
@@ -81716,16 +81774,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G734" s="5" t="n">
-        <v>0.022427</v>
-      </c>
-      <c r="H734" s="5" t="n">
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I734" s="5" t="n">
         <v>0.02243</v>
-      </c>
-      <c r="I734" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="J734" t="inlineStr">
         <is>
@@ -81801,7 +81861,7 @@
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>Sales and marketing</t>
+          <t>Sales and marketing (Note 17) 378,630</t>
         </is>
       </c>
       <c r="D735" t="inlineStr">
@@ -81809,22 +81869,28 @@
           <t>SellingAndMarketingExpense</t>
         </is>
       </c>
-      <c r="E735" s="5" t="n">
-        <v>0.27047</v>
-      </c>
-      <c r="F735" s="5" t="n">
-        <v>0.225895</v>
-      </c>
-      <c r="G735" s="5" t="n">
-        <v>0.475651</v>
-      </c>
-      <c r="H735" s="5" t="n">
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H735" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I735" s="5" t="n">
         <v>0.497923</v>
-      </c>
-      <c r="I735" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="J735" t="inlineStr">
         <is>
@@ -81895,12 +81961,12 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>Share‐based compensation                                      257,608                    ‐</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>Share‐based compensation                                      257,608                    ‐ total</t>
+          <t>Stock‐based compensation (Note 11) ‐</t>
         </is>
       </c>
       <c r="D736" t="inlineStr"/>
@@ -81914,16 +81980,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G736" s="5" t="n">
-        <v>5.683931</v>
-      </c>
-      <c r="H736" s="5" t="n">
-        <v>4.704404</v>
-      </c>
-      <c r="I736" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H736" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I736" s="5" t="n">
+        <v>0.257608</v>
       </c>
       <c r="J736" t="inlineStr">
         <is>
@@ -81994,19 +82062,15 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>Share‐based compensation                                      257,608                    ‐</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>Operating loss</t>
-        </is>
-      </c>
-      <c r="D737" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Operating loss (233,843)</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr"/>
       <c r="E737" t="inlineStr">
         <is>
           <t>-</t>
@@ -82017,16 +82081,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G737" s="5" t="n">
-        <v>-1.789102</v>
-      </c>
-      <c r="H737" s="5" t="n">
-        <v>-1.073513</v>
-      </c>
-      <c r="I737" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H737" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I737" s="5" t="n">
+        <v>-1.22089</v>
       </c>
       <c r="J737" t="inlineStr">
         <is>
@@ -82102,14 +82168,10 @@
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>Interest and bank charges (note 13)</t>
-        </is>
-      </c>
-      <c r="D738" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Finance expense (Note 8) 646,079</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr"/>
       <c r="E738" t="inlineStr">
         <is>
           <t>-</t>
@@ -82120,16 +82182,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G738" s="5" t="n">
-        <v>0.713347</v>
-      </c>
-      <c r="H738" s="5" t="n">
-        <v>0.742388</v>
-      </c>
-      <c r="I738" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H738" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I738" s="5" t="n">
+        <v>0.595011</v>
       </c>
       <c r="J738" t="inlineStr">
         <is>
@@ -82205,7 +82269,7 @@
       </c>
       <c r="C739" t="inlineStr">
         <is>
-          <t>Foreign exchange</t>
+          <t>Foreign exchange 116</t>
         </is>
       </c>
       <c r="D739" t="inlineStr">
@@ -82223,16 +82287,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G739" s="5" t="n">
-        <v>-0.012362</v>
-      </c>
-      <c r="H739" s="5" t="n">
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I739" s="5" t="n">
         <v>0.023576</v>
-      </c>
-      <c r="I739" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="J739" t="inlineStr">
         <is>
@@ -82308,7 +82374,7 @@
       </c>
       <c r="C740" t="inlineStr">
         <is>
-          <t>Gain on restructuring of trade payables (note 12)</t>
+          <t>Gain on sale of Kinzin shares (Note 13) ‐</t>
         </is>
       </c>
       <c r="D740" t="inlineStr"/>
@@ -82322,16 +82388,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G740" s="5" t="n">
-        <v>-0.414685</v>
-      </c>
-      <c r="H740" s="5" t="n">
-        <v>-0.101775</v>
-      </c>
-      <c r="I740" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H740" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I740" s="5" t="n">
+        <v>-0.018</v>
       </c>
       <c r="J740" t="inlineStr">
         <is>
@@ -82402,12 +82470,12 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>Loss attributable to parent                                      757,346                    ‐</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>Loss attributable to parent                                      757,346                    ‐ total</t>
+          <t>Gain on write‐up of Kinzin (Note 13) ‐</t>
         </is>
       </c>
       <c r="D741" t="inlineStr"/>
@@ -82421,16 +82489,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G741" s="5" t="n">
-        <v>5.752411</v>
-      </c>
-      <c r="H741" s="5" t="n">
-        <v>1.130192</v>
-      </c>
-      <c r="I741" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I741" s="5" t="n">
+        <v>-0.38</v>
       </c>
       <c r="J741" t="inlineStr">
         <is>
@@ -82501,12 +82571,12 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>Loss attributable to parent                                      757,346                    ‐</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>Loss before income taxes from continuing operations</t>
+          <t>Portion of equity loss on investment in Kinzin (Note 13) 273,343</t>
         </is>
       </c>
       <c r="D742" t="inlineStr"/>
@@ -82520,16 +82590,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G742" s="5" t="n">
-        <v>-7.541513</v>
-      </c>
-      <c r="H742" s="5" t="n">
-        <v>-2.203705</v>
-      </c>
-      <c r="I742" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H742" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I742" s="5" t="n">
+        <v>0.106657</v>
       </c>
       <c r="J742" t="inlineStr">
         <is>
@@ -82600,12 +82672,12 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>Income tax recovery                                                                                        ‐         47,482</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss from continuing operations</t>
+          <t>Discount and settlement on trade and other payables ‐</t>
         </is>
       </c>
       <c r="D743" t="inlineStr"/>
@@ -82619,16 +82691,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G743" s="5" t="n">
-        <v>-7.494031</v>
-      </c>
-      <c r="H743" s="5" t="n">
-        <v>-2.203705</v>
-      </c>
-      <c r="I743" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H743" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I743" s="5" t="n">
+        <v>-0.101775</v>
       </c>
       <c r="J743" t="inlineStr">
         <is>
@@ -82699,12 +82773,12 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>Income tax recovery                                                                                        ‐         47,482</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>Net (loss) income from discontinued operations, net of tax (note 5)</t>
+          <t>Loss attributable to parent (Note 13) ‐</t>
         </is>
       </c>
       <c r="D744" t="inlineStr"/>
@@ -82718,16 +82792,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G744" s="5" t="n">
-        <v>1.17218</v>
-      </c>
-      <c r="H744" s="5" t="n">
-        <v>-0.583008</v>
-      </c>
-      <c r="I744" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H744" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I744" s="5" t="n">
+        <v>0.757346</v>
       </c>
       <c r="J744" t="inlineStr">
         <is>
@@ -82798,19 +82874,15 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>Income tax recovery                                                                                        ‐         47,482</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>Net loss and total comprehensive loss</t>
-        </is>
-      </c>
-      <c r="D745" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Other expenses (income) total</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr"/>
       <c r="E745" t="inlineStr">
         <is>
           <t>-</t>
@@ -82821,16 +82893,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G745" s="5" t="n">
-        <v>-6.321851</v>
-      </c>
-      <c r="H745" s="5" t="n">
-        <v>-2.786713</v>
-      </c>
-      <c r="I745" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I745" s="5" t="n">
+        <v>0.982815</v>
       </c>
       <c r="J745" t="inlineStr">
         <is>
@@ -82901,12 +82975,12 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>Net loss and total comprehensive loss attributable to</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>Equity owners of Uniserve</t>
+          <t>Net loss from continuing operations (1,485,282)</t>
         </is>
       </c>
       <c r="D746" t="inlineStr"/>
@@ -82920,16 +82994,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G746" s="5" t="n">
-        <v>-4.71986</v>
-      </c>
-      <c r="H746" s="5" t="n">
-        <v>-2.786713</v>
-      </c>
-      <c r="I746" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I746" s="5" t="n">
+        <v>-2.203705</v>
       </c>
       <c r="J746" t="inlineStr">
         <is>
@@ -83000,17 +83076,17 @@
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>Non‐controlling interests                                                                                 ‐      (1,601,991)</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>Net loss and total comprehensive loss</t>
+          <t>Net loss from discontinued operations (Note 5) ‐</t>
         </is>
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>NetIncomeDiscontinuousOperations</t>
         </is>
       </c>
       <c r="E747" t="inlineStr">
@@ -83023,16 +83099,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G747" s="5" t="n">
-        <v>-6.321851</v>
-      </c>
-      <c r="H747" s="5" t="n">
-        <v>-2.786713</v>
-      </c>
-      <c r="I747" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H747" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I747" s="5" t="n">
+        <v>-0.583008</v>
       </c>
       <c r="J747" t="inlineStr">
         <is>
@@ -83103,12 +83181,12 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>Non‐controlling interests                                                                                 ‐      (1,601,991)</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share from continuing operations</t>
+          <t>Net loss and comprehensive loss (1,485,282)</t>
         </is>
       </c>
       <c r="D748" t="inlineStr"/>
@@ -83122,16 +83200,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G748" s="5" t="n">
-        <v>-2.6e-07</v>
-      </c>
-      <c r="H748" s="5" t="n">
-        <v>-7e-08</v>
-      </c>
-      <c r="I748" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I748" s="5" t="n">
+        <v>-2.786713</v>
       </c>
       <c r="J748" t="inlineStr">
         <is>
@@ -83202,12 +83282,12 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>Non‐controlling interests                                                                                 ‐      (1,601,991)</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share from discontinued operations</t>
+          <t>Basic and diluted loss per share from continuing operations $ (0.04) $</t>
         </is>
       </c>
       <c r="D749" t="inlineStr"/>
@@ -83221,16 +83301,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G749" s="5" t="n">
-        <v>4e-08</v>
-      </c>
-      <c r="H749" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="I749" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H749" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I749" s="5" t="n">
+        <v>-7e-08</v>
       </c>
       <c r="J749" t="inlineStr">
         <is>
@@ -83301,19 +83383,15 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>Non‐controlling interests                                                                                 ‐      (1,601,991)</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share</t>
-        </is>
-      </c>
-      <c r="D750" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Basic and diluted loss per share from discontinued operations $ ‐ $</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr"/>
       <c r="E750" t="inlineStr">
         <is>
           <t>-</t>
@@ -83324,16 +83402,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G750" s="5" t="n">
-        <v>-2.2e-07</v>
-      </c>
-      <c r="H750" s="5" t="n">
-        <v>-9e-08</v>
-      </c>
-      <c r="I750" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I750" s="5" t="n">
+        <v>-2e-08</v>
       </c>
       <c r="J750" t="inlineStr">
         <is>
@@ -83404,12 +83484,12 @@
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>Weighted average common shares, used in computing basic</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
         <is>
-          <t>Weighted average common shares, used in computing basic and diluted loss per share</t>
+          <t>Basic and diluted loss per share $ (0.04) $</t>
         </is>
       </c>
       <c r="D751" t="inlineStr">
@@ -83427,16 +83507,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G751" s="5" t="n">
-        <v>28.630835</v>
-      </c>
-      <c r="H751" s="5" t="n">
-        <v>30.091746</v>
-      </c>
-      <c r="I751" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H751" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I751" s="5" t="n">
+        <v>-9e-08</v>
       </c>
       <c r="J751" t="inlineStr">
         <is>
@@ -83507,17 +83589,17 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>As restated*</t>
+          <t>Weighted average number of common shares outstanding,</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
         <is>
-          <t>Revenues</t>
+          <t>Weighted average number of common shares outstanding, used in computing basic and diluted loss per share 37,591,045</t>
         </is>
       </c>
       <c r="D752" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E752" t="inlineStr">
@@ -83525,21 +83607,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F752" s="5" t="n">
-        <v>9.686593</v>
-      </c>
-      <c r="G752" s="5" t="n">
-        <v>8.161194</v>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H752" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I752" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I752" s="5" t="n">
+        <v>30.091746</v>
       </c>
       <c r="J752" t="inlineStr">
         <is>
@@ -83610,17 +83694,17 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>As restated*</t>
+          <t>Note 5 and 23</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>Cost of sales</t>
+          <t>Revenues</t>
         </is>
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>CostOfRevenue</t>
+          <t>TotalRevenue</t>
         </is>
       </c>
       <c r="E753" t="inlineStr">
@@ -83628,16 +83712,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F753" s="5" t="n">
-        <v>4.590626</v>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G753" s="5" t="n">
-        <v>4.266365</v>
-      </c>
-      <c r="H753" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>8.161194</v>
+      </c>
+      <c r="H753" s="5" t="n">
+        <v>7.372128</v>
       </c>
       <c r="I753" t="inlineStr">
         <is>
@@ -83713,30 +83797,34 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>As restated*</t>
+          <t>Note 5 and 23</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
         <is>
-          <t>As restated* total</t>
-        </is>
-      </c>
-      <c r="D754" t="inlineStr"/>
+          <t>Cost of revenues</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>CostOfRevenue</t>
+        </is>
+      </c>
       <c r="E754" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F754" s="5" t="n">
-        <v>5.095967</v>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G754" s="5" t="n">
-        <v>3.894829</v>
-      </c>
-      <c r="H754" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.266365</v>
+      </c>
+      <c r="H754" s="5" t="n">
+        <v>3.741237</v>
       </c>
       <c r="I754" t="inlineStr">
         <is>
@@ -83812,28 +83900,30 @@
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Note 5 and 23</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
         <is>
-          <t>Operations and service delivery costs</t>
+          <t>Note 5 and 23 total</t>
         </is>
       </c>
       <c r="D755" t="inlineStr"/>
-      <c r="E755" s="5" t="n">
-        <v>8.962754</v>
-      </c>
-      <c r="F755" s="5" t="n">
-        <v>4.778452</v>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G755" s="5" t="n">
-        <v>4.531915</v>
-      </c>
-      <c r="H755" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.894829</v>
+      </c>
+      <c r="H755" s="5" t="n">
+        <v>3.630891</v>
       </c>
       <c r="I755" t="inlineStr">
         <is>
@@ -83914,7 +84004,7 @@
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>Amortization of property and equipment (Note 6)</t>
+          <t>Operations and administration expenses</t>
         </is>
       </c>
       <c r="D756" t="inlineStr"/>
@@ -83923,16 +84013,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F756" s="5" t="n">
-        <v>0.41626</v>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G756" s="5" t="n">
-        <v>0.354236</v>
-      </c>
-      <c r="H756" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.531915</v>
+      </c>
+      <c r="H756" s="5" t="n">
+        <v>3.555414</v>
       </c>
       <c r="I756" t="inlineStr">
         <is>
@@ -84013,29 +84103,25 @@
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>Amortization of intangible assets (Note 7)</t>
-        </is>
-      </c>
-      <c r="D757" t="inlineStr">
-        <is>
-          <t>DepreciationAmortizationDepletion</t>
-        </is>
-      </c>
+          <t>Amortization of property and equipment (note 7)</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr"/>
       <c r="E757" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F757" s="5" t="n">
-        <v>0.44</v>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G757" s="5" t="n">
-        <v>0.299702</v>
-      </c>
-      <c r="H757" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.354236</v>
+      </c>
+      <c r="H757" s="5" t="n">
+        <v>0.358557</v>
       </c>
       <c r="I757" t="inlineStr">
         <is>
@@ -84116,25 +84202,29 @@
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>Amortization of deferred finance costs</t>
-        </is>
-      </c>
-      <c r="D758" t="inlineStr"/>
+          <t>Amortization of intangible assets (note 8)</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E758" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F758" s="5" t="n">
-        <v>0.008515</v>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G758" s="5" t="n">
-        <v>0.022427</v>
-      </c>
-      <c r="H758" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.299702</v>
+      </c>
+      <c r="H758" s="5" t="n">
+        <v>0.012472</v>
       </c>
       <c r="I758" t="inlineStr">
         <is>
@@ -84215,29 +84305,25 @@
       </c>
       <c r="C759" t="inlineStr">
         <is>
-          <t>Operating loss</t>
-        </is>
-      </c>
-      <c r="D759" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Amortization of deferred finance costs (note 8)</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr"/>
       <c r="E759" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F759" s="5" t="n">
-        <v>-0.773155</v>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G759" s="5" t="n">
-        <v>-1.789102</v>
-      </c>
-      <c r="H759" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.022427</v>
+      </c>
+      <c r="H759" s="5" t="n">
+        <v>0.02243</v>
       </c>
       <c r="I759" t="inlineStr">
         <is>
@@ -84313,32 +84399,30 @@
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>Interest and bank charges</t>
+          <t>Sales and marketing</t>
         </is>
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>SellingAndMarketingExpense</t>
         </is>
       </c>
       <c r="E760" s="5" t="n">
-        <v>1.381965</v>
+        <v>0.27047</v>
       </c>
       <c r="F760" s="5" t="n">
-        <v>0.631154</v>
+        <v>0.225895</v>
       </c>
       <c r="G760" s="5" t="n">
-        <v>0.713347</v>
-      </c>
-      <c r="H760" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.475651</v>
+      </c>
+      <c r="H760" s="5" t="n">
+        <v>0.497923</v>
       </c>
       <c r="I760" t="inlineStr">
         <is>
@@ -84414,34 +84498,30 @@
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Share‐based compensation                                      257,608                    ‐</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>Foreign exchange gain (loss)</t>
-        </is>
-      </c>
-      <c r="D761" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Share‐based compensation                                      257,608                    ‐ total</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr"/>
       <c r="E761" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F761" s="5" t="n">
-        <v>-0.063832</v>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G761" s="5" t="n">
-        <v>0.012362</v>
-      </c>
-      <c r="H761" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.683931</v>
+      </c>
+      <c r="H761" s="5" t="n">
+        <v>4.704404</v>
       </c>
       <c r="I761" t="inlineStr">
         <is>
@@ -84517,15 +84597,19 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Share‐based compensation                                      257,608                    ‐</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
         <is>
-          <t>Writedown of intangible assets (Note 7)</t>
-        </is>
-      </c>
-      <c r="D762" t="inlineStr"/>
+          <t>Operating loss</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E762" t="inlineStr">
         <is>
           <t>-</t>
@@ -84537,12 +84621,10 @@
         </is>
       </c>
       <c r="G762" s="5" t="n">
-        <v>-2.277281</v>
-      </c>
-      <c r="H762" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.789102</v>
+      </c>
+      <c r="H762" s="5" t="n">
+        <v>-1.073513</v>
       </c>
       <c r="I762" t="inlineStr">
         <is>
@@ -84618,15 +84700,19 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
         <is>
-          <t>Write-down of goodwill (Notes 8)</t>
-        </is>
-      </c>
-      <c r="D763" t="inlineStr"/>
+          <t>Interest and bank charges (note 13)</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E763" t="inlineStr">
         <is>
           <t>-</t>
@@ -84638,12 +84724,10 @@
         </is>
       </c>
       <c r="G763" s="5" t="n">
-        <v>-2.301224</v>
-      </c>
-      <c r="H763" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.713347</v>
+      </c>
+      <c r="H763" s="5" t="n">
+        <v>0.742388</v>
       </c>
       <c r="I763" t="inlineStr">
         <is>
@@ -84719,32 +84803,34 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>Write-down of capital assets (Note 6)</t>
-        </is>
-      </c>
-      <c r="D764" t="inlineStr"/>
+          <t>Foreign exchange</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>ForeignExchangeTradingGains</t>
+        </is>
+      </c>
       <c r="E764" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F764" s="5" t="n">
-        <v>-0.034372</v>
-      </c>
-      <c r="G764" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H764" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G764" s="5" t="n">
+        <v>-0.012362</v>
+      </c>
+      <c r="H764" s="5" t="n">
+        <v>0.023576</v>
       </c>
       <c r="I764" t="inlineStr">
         <is>
@@ -84820,12 +84906,12 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
         <is>
-          <t>Gain on restructuring of accounts payable (Note 11)</t>
+          <t>Gain on restructuring of trade payables (note 12)</t>
         </is>
       </c>
       <c r="D765" t="inlineStr"/>
@@ -84834,16 +84920,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F765" s="5" t="n">
-        <v>1.318442</v>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G765" s="5" t="n">
-        <v>0.414685</v>
-      </c>
-      <c r="H765" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.414685</v>
+      </c>
+      <c r="H765" s="5" t="n">
+        <v>-0.101775</v>
       </c>
       <c r="I765" t="inlineStr">
         <is>
@@ -84919,12 +85005,12 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Loss attributable to parent                                      757,346                    ‐</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>Gain on restructuring of preferred shares (Note 12)</t>
+          <t>Loss attributable to parent                                      757,346                    ‐ total</t>
         </is>
       </c>
       <c r="D766" t="inlineStr"/>
@@ -84933,18 +85019,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F766" s="5" t="n">
-        <v>1.048466</v>
-      </c>
-      <c r="G766" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H766" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F766" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G766" s="5" t="n">
+        <v>5.752411</v>
+      </c>
+      <c r="H766" s="5" t="n">
+        <v>1.130192</v>
       </c>
       <c r="I766" t="inlineStr">
         <is>
@@ -85020,12 +85104,12 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Loss attributable to parent                                      757,346                    ‐</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
         <is>
-          <t>Gain on sale of KBT (Note 4)</t>
+          <t>Loss before income taxes from continuing operations</t>
         </is>
       </c>
       <c r="D767" t="inlineStr"/>
@@ -85040,12 +85124,10 @@
         </is>
       </c>
       <c r="G767" s="5" t="n">
-        <v>0.220521</v>
-      </c>
-      <c r="H767" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-7.541513</v>
+      </c>
+      <c r="H767" s="5" t="n">
+        <v>-2.203705</v>
       </c>
       <c r="I767" t="inlineStr">
         <is>
@@ -85121,12 +85203,12 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Income tax recovery                                                                                        ‐         47,482</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
         <is>
-          <t>Accretion to face value of preferred shares (Note 12)</t>
+          <t>Net loss and comprehensive loss from continuing operations</t>
         </is>
       </c>
       <c r="D768" t="inlineStr"/>
@@ -85135,16 +85217,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F768" s="5" t="n">
-        <v>-0.309282</v>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G768" s="5" t="n">
-        <v>-0.447456</v>
-      </c>
-      <c r="H768" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-7.494031</v>
+      </c>
+      <c r="H768" s="5" t="n">
+        <v>-2.203705</v>
       </c>
       <c r="I768" t="inlineStr">
         <is>
@@ -85220,12 +85302,12 @@
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Income tax recovery                                                                                        ‐         47,482</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>Dilution gain (loss) (Note 15)</t>
+          <t>Net (loss) income from discontinued operations, net of tax (note 5)</t>
         </is>
       </c>
       <c r="D769" t="inlineStr"/>
@@ -85234,16 +85316,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F769" s="5" t="n">
-        <v>-0.15188</v>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G769" s="5" t="n">
-        <v>0.06410399999999999</v>
-      </c>
-      <c r="H769" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.17218</v>
+      </c>
+      <c r="H769" s="5" t="n">
+        <v>-0.583008</v>
       </c>
       <c r="I769" t="inlineStr">
         <is>
@@ -85319,28 +85401,34 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Income tax recovery                                                                                        ‐         47,482</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>Other income (expense) total</t>
-        </is>
-      </c>
-      <c r="D770" t="inlineStr"/>
-      <c r="E770" s="5" t="n">
-        <v>-3.36116</v>
-      </c>
-      <c r="F770" s="5" t="n">
-        <v>1.176388</v>
+          <t>Net loss and total comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F770" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G770" s="5" t="n">
-        <v>-5.027636</v>
-      </c>
-      <c r="H770" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-6.321851</v>
+      </c>
+      <c r="H770" s="5" t="n">
+        <v>-2.786713</v>
       </c>
       <c r="I770" t="inlineStr">
         <is>
@@ -85416,12 +85504,12 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Net loss and total comprehensive loss attributable to</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
         <is>
-          <t>(Loss) income before income taxes from continuing operations</t>
+          <t>Equity owners of Uniserve</t>
         </is>
       </c>
       <c r="D771" t="inlineStr"/>
@@ -85430,16 +85518,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F771" s="5" t="n">
-        <v>0.403233</v>
+      <c r="F771" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G771" s="5" t="n">
-        <v>-6.816738</v>
-      </c>
-      <c r="H771" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4.71986</v>
+      </c>
+      <c r="H771" s="5" t="n">
+        <v>-2.786713</v>
       </c>
       <c r="I771" t="inlineStr">
         <is>
@@ -85515,28 +85603,34 @@
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>Income tax recovery</t>
+          <t>Non‐controlling interests                                                                                 ‐      (1,601,991)</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
         <is>
-          <t>Future</t>
-        </is>
-      </c>
-      <c r="D772" t="inlineStr"/>
-      <c r="E772" s="5" t="n">
-        <v>0.064341</v>
-      </c>
-      <c r="F772" s="5" t="n">
-        <v>0.063902</v>
+          <t>Net loss and total comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G772" s="5" t="n">
-        <v>0.047482</v>
-      </c>
-      <c r="H772" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-6.321851</v>
+      </c>
+      <c r="H772" s="5" t="n">
+        <v>-2.786713</v>
       </c>
       <c r="I772" t="inlineStr">
         <is>
@@ -85612,12 +85706,12 @@
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>Income tax recovery</t>
+          <t>Non‐controlling interests                                                                                 ‐      (1,601,991)</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>Net (loss) income and comprehensive (loss) income for the year</t>
+          <t>Basic and diluted loss per share from continuing operations</t>
         </is>
       </c>
       <c r="D773" t="inlineStr"/>
@@ -85626,16 +85720,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F773" s="5" t="n">
-        <v>0.467135</v>
+      <c r="F773" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G773" s="5" t="n">
-        <v>-6.769256</v>
-      </c>
-      <c r="H773" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.6e-07</v>
+      </c>
+      <c r="H773" s="5" t="n">
+        <v>-7e-08</v>
       </c>
       <c r="I773" t="inlineStr">
         <is>
@@ -85711,12 +85805,12 @@
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>Income tax recovery</t>
+          <t>Non‐controlling interests                                                                                 ‐      (1,601,991)</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
         <is>
-          <t>Net income from discontinued operations, net of tax (Note 4)</t>
+          <t>Basic and diluted loss per share from discontinued operations</t>
         </is>
       </c>
       <c r="D774" t="inlineStr"/>
@@ -85725,16 +85819,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F774" s="5" t="n">
-        <v>0.784005</v>
+      <c r="F774" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G774" s="5" t="n">
-        <v>0.951659</v>
-      </c>
-      <c r="H774" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4e-08</v>
+      </c>
+      <c r="H774" s="5" t="n">
+        <v>-2e-08</v>
       </c>
       <c r="I774" t="inlineStr">
         <is>
@@ -85810,30 +85904,34 @@
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>Income tax recovery</t>
+          <t>Non‐controlling interests                                                                                 ‐      (1,601,991)</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
         <is>
-          <t>Common shareholders</t>
-        </is>
-      </c>
-      <c r="D775" t="inlineStr"/>
+          <t>Basic and diluted loss per share</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E775" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F775" s="5" t="n">
-        <v>1.25114</v>
+      <c r="F775" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G775" s="5" t="n">
-        <v>-4.215606</v>
-      </c>
-      <c r="H775" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.2e-07</v>
+      </c>
+      <c r="H775" s="5" t="n">
+        <v>-9e-08</v>
       </c>
       <c r="I775" t="inlineStr">
         <is>
@@ -85909,17 +86007,17 @@
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>Income tax recovery</t>
+          <t>Weighted average common shares, used in computing basic</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
         <is>
-          <t>Non-controlling interests (Note 15)</t>
+          <t>Weighted average common shares, used in computing basic and diluted loss per share</t>
         </is>
       </c>
       <c r="D776" t="inlineStr">
         <is>
-          <t>MinorityInterests</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E776" t="inlineStr">
@@ -85933,12 +86031,10 @@
         </is>
       </c>
       <c r="G776" s="5" t="n">
-        <v>1.601991</v>
-      </c>
-      <c r="H776" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>28.630835</v>
+      </c>
+      <c r="H776" s="5" t="n">
+        <v>30.091746</v>
       </c>
       <c r="I776" t="inlineStr">
         <is>
@@ -86014,23 +86110,29 @@
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>Income tax recovery</t>
+          <t>As restated*</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
         <is>
-          <t>Income tax recovery total</t>
-        </is>
-      </c>
-      <c r="D777" t="inlineStr"/>
-      <c r="E777" s="5" t="n">
-        <v>0.433699</v>
+          <t>Revenues</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E777" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F777" s="5" t="n">
-        <v>1.25114</v>
+        <v>9.686593</v>
       </c>
       <c r="G777" s="5" t="n">
-        <v>-5.817597</v>
+        <v>8.161194</v>
       </c>
       <c r="H777" t="inlineStr">
         <is>
@@ -86111,25 +86213,29 @@
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>Loss per share</t>
+          <t>As restated*</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
         <is>
-          <t>Basic (loss) earnings per share from continuing operations</t>
-        </is>
-      </c>
-      <c r="D778" t="inlineStr"/>
+          <t>Cost of sales</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>CostOfRevenue</t>
+        </is>
+      </c>
       <c r="E778" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F778" s="5" t="n">
-        <v>2e-08</v>
+        <v>4.590626</v>
       </c>
       <c r="G778" s="5" t="n">
-        <v>-2.4e-07</v>
+        <v>4.266365</v>
       </c>
       <c r="H778" t="inlineStr">
         <is>
@@ -86210,12 +86316,12 @@
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>Loss per share</t>
+          <t>As restated*</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>Basic (loss) earnings per share (1)</t>
+          <t>As restated* total</t>
         </is>
       </c>
       <c r="D779" t="inlineStr"/>
@@ -86225,10 +86331,10 @@
         </is>
       </c>
       <c r="F779" s="5" t="n">
-        <v>5e-08</v>
+        <v>5.095967</v>
       </c>
       <c r="G779" s="5" t="n">
-        <v>-2e-07</v>
+        <v>3.894829</v>
       </c>
       <c r="H779" t="inlineStr">
         <is>
@@ -86309,25 +86415,23 @@
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>Loss per share</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
         <is>
-          <t>Diluted (loss) earnings per share from continuing operations</t>
+          <t>Operations and service delivery costs</t>
         </is>
       </c>
       <c r="D780" t="inlineStr"/>
-      <c r="E780" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E780" s="5" t="n">
+        <v>8.962754</v>
       </c>
       <c r="F780" s="5" t="n">
-        <v>1e-08</v>
+        <v>4.778452</v>
       </c>
       <c r="G780" s="5" t="n">
-        <v>-2.4e-07</v>
+        <v>4.531915</v>
       </c>
       <c r="H780" t="inlineStr">
         <is>
@@ -86408,12 +86512,12 @@
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>Loss per share</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
         <is>
-          <t>Diluted (loss) earnings per share (1)</t>
+          <t>Amortization of property and equipment (Note 6)</t>
         </is>
       </c>
       <c r="D781" t="inlineStr"/>
@@ -86423,10 +86527,10 @@
         </is>
       </c>
       <c r="F781" s="5" t="n">
-        <v>4e-08</v>
+        <v>0.41626</v>
       </c>
       <c r="G781" s="5" t="n">
-        <v>-2e-07</v>
+        <v>0.354236</v>
       </c>
       <c r="H781" t="inlineStr">
         <is>
@@ -86507,17 +86611,17 @@
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>Loss per share</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding - basic</t>
+          <t>Amortization of intangible assets (Note 7)</t>
         </is>
       </c>
       <c r="D782" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E782" t="inlineStr">
@@ -86526,10 +86630,10 @@
         </is>
       </c>
       <c r="F782" s="5" t="n">
-        <v>25.891139</v>
+        <v>0.44</v>
       </c>
       <c r="G782" s="5" t="n">
-        <v>28.630835</v>
+        <v>0.299702</v>
       </c>
       <c r="H782" t="inlineStr">
         <is>
@@ -86610,29 +86714,25 @@
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>Loss per share</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding - diluted</t>
-        </is>
-      </c>
-      <c r="D783" t="inlineStr">
-        <is>
-          <t>DilutedAverageShares</t>
-        </is>
-      </c>
+          <t>Amortization of deferred finance costs</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr"/>
       <c r="E783" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F783" s="5" t="n">
-        <v>34.121519</v>
+        <v>0.008515</v>
       </c>
       <c r="G783" s="5" t="n">
-        <v>28.630835</v>
+        <v>0.022427</v>
       </c>
       <c r="H783" t="inlineStr">
         <is>
@@ -86711,27 +86811,31 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B784" t="inlineStr"/>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
       <c r="C784" t="inlineStr">
         <is>
-          <t>Revenues</t>
+          <t>Operating loss</t>
         </is>
       </c>
       <c r="D784" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
-      <c r="E784" s="5" t="n">
-        <v>18.637624</v>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E784" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F784" s="5" t="n">
-        <v>14.849741</v>
-      </c>
-      <c r="G784" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.773155</v>
+      </c>
+      <c r="G784" s="5" t="n">
+        <v>-1.789102</v>
       </c>
       <c r="H784" t="inlineStr">
         <is>
@@ -86810,27 +86914,29 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B785" t="inlineStr"/>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>Other income (expense)</t>
+        </is>
+      </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>Cost of sales</t>
+          <t>Interest and bank charges</t>
         </is>
       </c>
       <c r="D785" t="inlineStr">
         <is>
-          <t>CostOfRevenue</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E785" s="5" t="n">
-        <v>9.594476</v>
+        <v>1.381965</v>
       </c>
       <c r="F785" s="5" t="n">
-        <v>7.593671</v>
-      </c>
-      <c r="G785" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.631154</v>
+      </c>
+      <c r="G785" s="5" t="n">
+        <v>0.713347</v>
       </c>
       <c r="H785" t="inlineStr">
         <is>
@@ -86909,27 +87015,31 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B786" t="inlineStr"/>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>Other income (expense)</t>
+        </is>
+      </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>Gross margin</t>
+          <t>Foreign exchange gain (loss)</t>
         </is>
       </c>
       <c r="D786" t="inlineStr">
         <is>
-          <t>GrossProfit</t>
-        </is>
-      </c>
-      <c r="E786" s="5" t="n">
-        <v>9.043148</v>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E786" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F786" s="5" t="n">
-        <v>7.25607</v>
-      </c>
-      <c r="G786" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.063832</v>
+      </c>
+      <c r="G786" s="5" t="n">
+        <v>0.012362</v>
       </c>
       <c r="H786" t="inlineStr">
         <is>
@@ -87010,25 +87120,27 @@
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
         <is>
-          <t>Amortization of property and equipment (Note 5)</t>
+          <t>Writedown of intangible assets (Note 7)</t>
         </is>
       </c>
       <c r="D787" t="inlineStr"/>
-      <c r="E787" s="5" t="n">
-        <v>0.834015</v>
-      </c>
-      <c r="F787" s="5" t="n">
-        <v>0.511518</v>
-      </c>
-      <c r="G787" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E787" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G787" s="5" t="n">
+        <v>-2.277281</v>
       </c>
       <c r="H787" t="inlineStr">
         <is>
@@ -87109,29 +87221,27 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
         <is>
-          <t>Amortization of intangible assets (Note 6)</t>
-        </is>
-      </c>
-      <c r="D788" t="inlineStr">
-        <is>
-          <t>DepreciationAmortizationDepletion</t>
-        </is>
-      </c>
-      <c r="E788" s="5" t="n">
-        <v>0.554725</v>
-      </c>
-      <c r="F788" s="5" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="G788" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Write-down of goodwill (Notes 8)</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr"/>
+      <c r="E788" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G788" s="5" t="n">
+        <v>-2.301224</v>
       </c>
       <c r="H788" t="inlineStr">
         <is>
@@ -87212,22 +87322,22 @@
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>Stock-based compensation (Note 12(c))</t>
+          <t>Write-down of capital assets (Note 6)</t>
         </is>
       </c>
       <c r="D789" t="inlineStr"/>
-      <c r="E789" s="5" t="n">
-        <v>0.003969</v>
-      </c>
-      <c r="F789" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E789" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F789" s="5" t="n">
+        <v>-0.034372</v>
       </c>
       <c r="G789" t="inlineStr">
         <is>
@@ -87313,29 +87423,25 @@
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
         <is>
-          <t>Operating income (loss)</t>
-        </is>
-      </c>
-      <c r="D790" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
-      <c r="E790" s="5" t="n">
-        <v>-1.582785</v>
+          <t>Gain on restructuring of accounts payable (Note 11)</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr"/>
+      <c r="E790" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F790" s="5" t="n">
-        <v>0.169828</v>
-      </c>
-      <c r="G790" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.318442</v>
+      </c>
+      <c r="G790" s="5" t="n">
+        <v>0.414685</v>
       </c>
       <c r="H790" t="inlineStr">
         <is>
@@ -87421,19 +87527,17 @@
       </c>
       <c r="C791" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
-        </is>
-      </c>
-      <c r="D791" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E791" s="5" t="n">
-        <v>-1.289519</v>
+          <t>Gain on restructuring of preferred shares (Note 12)</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr"/>
+      <c r="E791" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F791" s="5" t="n">
-        <v>-0.063832</v>
+        <v>1.048466</v>
       </c>
       <c r="G791" t="inlineStr">
         <is>
@@ -87524,22 +87628,22 @@
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>Write-down of goodwill and intangible assets (Notes 6, 7)</t>
+          <t>Gain on sale of KBT (Note 4)</t>
         </is>
       </c>
       <c r="D792" t="inlineStr"/>
-      <c r="E792" s="5" t="n">
-        <v>-0.411146</v>
+      <c r="E792" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F792" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G792" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G792" s="5" t="n">
+        <v>0.220521</v>
       </c>
       <c r="H792" t="inlineStr">
         <is>
@@ -87625,20 +87729,20 @@
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>Write-down of capital assets (Note 5)</t>
+          <t>Accretion to face value of preferred shares (Note 12)</t>
         </is>
       </c>
       <c r="D793" t="inlineStr"/>
-      <c r="E793" s="5" t="n">
-        <v>-0.041318</v>
+      <c r="E793" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F793" s="5" t="n">
-        <v>-0.034372</v>
-      </c>
-      <c r="G793" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.309282</v>
+      </c>
+      <c r="G793" s="5" t="n">
+        <v>-0.447456</v>
       </c>
       <c r="H793" t="inlineStr">
         <is>
@@ -87724,7 +87828,7 @@
       </c>
       <c r="C794" t="inlineStr">
         <is>
-          <t>Gain on restructuring of accounts payable (Note 10)</t>
+          <t>Dilution gain (loss) (Note 15)</t>
         </is>
       </c>
       <c r="D794" t="inlineStr"/>
@@ -87734,12 +87838,10 @@
         </is>
       </c>
       <c r="F794" s="5" t="n">
-        <v>1.318442</v>
-      </c>
-      <c r="G794" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.15188</v>
+      </c>
+      <c r="G794" s="5" t="n">
+        <v>0.06410399999999999</v>
       </c>
       <c r="H794" t="inlineStr">
         <is>
@@ -87825,22 +87927,18 @@
       </c>
       <c r="C795" t="inlineStr">
         <is>
-          <t>Gain on restructuring of preferred shares (Note 11)</t>
+          <t>Other income (expense) total</t>
         </is>
       </c>
       <c r="D795" t="inlineStr"/>
-      <c r="E795" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E795" s="5" t="n">
+        <v>-3.36116</v>
       </c>
       <c r="F795" s="5" t="n">
-        <v>1.048466</v>
-      </c>
-      <c r="G795" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.176388</v>
+      </c>
+      <c r="G795" s="5" t="n">
+        <v>-5.027636</v>
       </c>
       <c r="H795" t="inlineStr">
         <is>
@@ -87926,20 +88024,20 @@
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>Accretion to face value of preferred shares (Note 11)</t>
+          <t>(Loss) income before income taxes from continuing operations</t>
         </is>
       </c>
       <c r="D796" t="inlineStr"/>
-      <c r="E796" s="5" t="n">
-        <v>-0.237212</v>
+      <c r="E796" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F796" s="5" t="n">
-        <v>-0.309282</v>
-      </c>
-      <c r="G796" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.403233</v>
+      </c>
+      <c r="G796" s="5" t="n">
+        <v>-6.816738</v>
       </c>
       <c r="H796" t="inlineStr">
         <is>
@@ -88020,27 +88118,23 @@
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Income tax recovery</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
         <is>
-          <t>Dilution loss (Note 14)</t>
+          <t>Future</t>
         </is>
       </c>
       <c r="D797" t="inlineStr"/>
-      <c r="E797" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E797" s="5" t="n">
+        <v>0.064341</v>
       </c>
       <c r="F797" s="5" t="n">
-        <v>-0.15188</v>
-      </c>
-      <c r="G797" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.063902</v>
+      </c>
+      <c r="G797" s="5" t="n">
+        <v>0.047482</v>
       </c>
       <c r="H797" t="inlineStr">
         <is>
@@ -88121,29 +88215,25 @@
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Income tax recovery</t>
         </is>
       </c>
       <c r="C798" t="inlineStr">
         <is>
-          <t>Income (loss) before income taxes</t>
-        </is>
-      </c>
-      <c r="D798" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
-      <c r="E798" s="5" t="n">
-        <v>-4.943945</v>
+          <t>Net (loss) income and comprehensive (loss) income for the year</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr"/>
+      <c r="E798" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F798" s="5" t="n">
-        <v>1.180604</v>
-      </c>
-      <c r="G798" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.467135</v>
+      </c>
+      <c r="G798" s="5" t="n">
+        <v>-6.769256</v>
       </c>
       <c r="H798" t="inlineStr">
         <is>
@@ -88229,22 +88319,20 @@
       </c>
       <c r="C799" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Net income from discontinued operations, net of tax (Note 4)</t>
         </is>
       </c>
       <c r="D799" t="inlineStr"/>
-      <c r="E799" s="5" t="n">
-        <v>0.369358</v>
-      </c>
-      <c r="F799" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G799" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F799" s="5" t="n">
+        <v>0.784005</v>
+      </c>
+      <c r="G799" s="5" t="n">
+        <v>0.951659</v>
       </c>
       <c r="H799" t="inlineStr">
         <is>
@@ -88330,20 +88418,20 @@
       </c>
       <c r="C800" t="inlineStr">
         <is>
-          <t>Net income (loss) and comprehensive income (loss) for the year from continuing operations</t>
+          <t>Common shareholders</t>
         </is>
       </c>
       <c r="D800" t="inlineStr"/>
-      <c r="E800" s="5" t="n">
-        <v>-4.510246</v>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F800" s="5" t="n">
         <v>1.25114</v>
       </c>
-      <c r="G800" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G800" s="5" t="n">
+        <v>-4.215606</v>
       </c>
       <c r="H800" t="inlineStr">
         <is>
@@ -88429,22 +88517,26 @@
       </c>
       <c r="C801" t="inlineStr">
         <is>
-          <t>Results from discontinued operations (Note 4)</t>
-        </is>
-      </c>
-      <c r="D801" t="inlineStr"/>
-      <c r="E801" s="5" t="n">
-        <v>4.418501</v>
+          <t>Non-controlling interests (Note 15)</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>MinorityInterests</t>
+        </is>
+      </c>
+      <c r="E801" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F801" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G801" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G801" s="5" t="n">
+        <v>1.601991</v>
       </c>
       <c r="H801" t="inlineStr">
         <is>
@@ -88530,24 +88622,18 @@
       </c>
       <c r="C802" t="inlineStr">
         <is>
-          <t>Net income (loss) and comprehensive income (loss) for the year</t>
-        </is>
-      </c>
-      <c r="D802" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Income tax recovery total</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr"/>
       <c r="E802" s="5" t="n">
-        <v>-0.09174499999999999</v>
+        <v>0.433699</v>
       </c>
       <c r="F802" s="5" t="n">
         <v>1.25114</v>
       </c>
-      <c r="G802" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G802" s="5" t="n">
+        <v>-5.817597</v>
       </c>
       <c r="H802" t="inlineStr">
         <is>
@@ -88628,25 +88714,25 @@
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>Earning per share</t>
+          <t>Loss per share</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
         <is>
-          <t>Basic earnings (loss) per share from continuing operations</t>
+          <t>Basic (loss) earnings per share from continuing operations</t>
         </is>
       </c>
       <c r="D803" t="inlineStr"/>
-      <c r="E803" s="5" t="n">
-        <v>-1.8e-07</v>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F803" s="5" t="n">
-        <v>5e-08</v>
-      </c>
-      <c r="G803" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2e-08</v>
+      </c>
+      <c r="G803" s="5" t="n">
+        <v>-2.4e-07</v>
       </c>
       <c r="H803" t="inlineStr">
         <is>
@@ -88727,29 +88813,25 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>Earning per share</t>
+          <t>Loss per share</t>
         </is>
       </c>
       <c r="C804" t="inlineStr">
         <is>
-          <t>Basic earnings (loss) per share</t>
-        </is>
-      </c>
-      <c r="D804" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E804" s="5" t="n">
-        <v>0</v>
+          <t>Basic (loss) earnings per share (1)</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr"/>
+      <c r="E804" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F804" s="5" t="n">
         <v>5e-08</v>
       </c>
-      <c r="G804" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G804" s="5" t="n">
+        <v>-2e-07</v>
       </c>
       <c r="H804" t="inlineStr">
         <is>
@@ -88830,25 +88912,25 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>Earning per share</t>
+          <t>Loss per share</t>
         </is>
       </c>
       <c r="C805" t="inlineStr">
         <is>
-          <t>Diluted earnings (loss) per share from continuing operations (1)</t>
+          <t>Diluted (loss) earnings per share from continuing operations</t>
         </is>
       </c>
       <c r="D805" t="inlineStr"/>
-      <c r="E805" s="5" t="n">
-        <v>-1.8e-07</v>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F805" s="5" t="n">
-        <v>4e-08</v>
-      </c>
-      <c r="G805" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1e-08</v>
+      </c>
+      <c r="G805" s="5" t="n">
+        <v>-2.4e-07</v>
       </c>
       <c r="H805" t="inlineStr">
         <is>
@@ -88929,25 +89011,25 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>Earning per share</t>
+          <t>Loss per share</t>
         </is>
       </c>
       <c r="C806" t="inlineStr">
         <is>
-          <t>Diluted earnings (loss) per share (1)</t>
+          <t>Diluted (loss) earnings per share (1)</t>
         </is>
       </c>
       <c r="D806" t="inlineStr"/>
-      <c r="E806" s="5" t="n">
-        <v>0</v>
+      <c r="E806" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F806" s="5" t="n">
         <v>4e-08</v>
       </c>
-      <c r="G806" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G806" s="5" t="n">
+        <v>-2e-07</v>
       </c>
       <c r="H806" t="inlineStr">
         <is>
@@ -89028,7 +89110,7 @@
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>Earning per share</t>
+          <t>Loss per share</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
@@ -89041,16 +89123,16 @@
           <t>BasicAverageShares</t>
         </is>
       </c>
-      <c r="E807" s="5" t="n">
-        <v>24.609495</v>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F807" s="5" t="n">
         <v>25.891139</v>
       </c>
-      <c r="G807" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G807" s="5" t="n">
+        <v>28.630835</v>
       </c>
       <c r="H807" t="inlineStr">
         <is>
@@ -89131,7 +89213,7 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>Earning per share</t>
+          <t>Loss per share</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
@@ -89144,16 +89226,16 @@
           <t>DilutedAverageShares</t>
         </is>
       </c>
-      <c r="E808" s="5" t="n">
-        <v>24.609495</v>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F808" s="5" t="n">
         <v>34.121519</v>
       </c>
-      <c r="G808" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G808" s="5" t="n">
+        <v>28.630835</v>
       </c>
       <c r="H808" t="inlineStr">
         <is>
@@ -89221,6 +89303,2527 @@
         </is>
       </c>
       <c r="U808" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr"/>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>Revenues</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E809" s="5" t="n">
+        <v>18.637624</v>
+      </c>
+      <c r="F809" s="5" t="n">
+        <v>14.849741</v>
+      </c>
+      <c r="G809" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H809" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I809" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J809" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K809" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L809" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M809" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N809" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O809" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P809" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q809" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R809" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S809" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T809" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U809" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr"/>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>Cost of sales</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>CostOfRevenue</t>
+        </is>
+      </c>
+      <c r="E810" s="5" t="n">
+        <v>9.594476</v>
+      </c>
+      <c r="F810" s="5" t="n">
+        <v>7.593671</v>
+      </c>
+      <c r="G810" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H810" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I810" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J810" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K810" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L810" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M810" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N810" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O810" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P810" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q810" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R810" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S810" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T810" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U810" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr"/>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>GrossProfit</t>
+        </is>
+      </c>
+      <c r="E811" s="5" t="n">
+        <v>9.043148</v>
+      </c>
+      <c r="F811" s="5" t="n">
+        <v>7.25607</v>
+      </c>
+      <c r="G811" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H811" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I811" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J811" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K811" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L811" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M811" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N811" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O811" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P811" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q811" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R811" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S811" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T811" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U811" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>Amortization of property and equipment (Note 5)</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr"/>
+      <c r="E812" s="5" t="n">
+        <v>0.834015</v>
+      </c>
+      <c r="F812" s="5" t="n">
+        <v>0.511518</v>
+      </c>
+      <c r="G812" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H812" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I812" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J812" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K812" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L812" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M812" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N812" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O812" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P812" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q812" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R812" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S812" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T812" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U812" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>Amortization of intangible assets (Note 6)</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
+      <c r="E813" s="5" t="n">
+        <v>0.554725</v>
+      </c>
+      <c r="F813" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="G813" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H813" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I813" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J813" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K813" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L813" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M813" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N813" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O813" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P813" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q813" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R813" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S813" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T813" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U813" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>Stock-based compensation (Note 12(c))</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr"/>
+      <c r="E814" s="5" t="n">
+        <v>0.003969</v>
+      </c>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G814" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H814" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I814" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J814" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K814" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L814" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M814" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N814" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O814" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P814" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q814" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R814" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S814" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T814" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U814" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>Operating income (loss)</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E815" s="5" t="n">
+        <v>-1.582785</v>
+      </c>
+      <c r="F815" s="5" t="n">
+        <v>0.169828</v>
+      </c>
+      <c r="G815" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H815" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I815" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J815" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K815" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L815" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M815" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N815" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O815" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P815" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q815" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R815" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S815" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T815" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U815" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>Other income (expense)</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E816" s="5" t="n">
+        <v>-1.289519</v>
+      </c>
+      <c r="F816" s="5" t="n">
+        <v>-0.063832</v>
+      </c>
+      <c r="G816" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H816" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I816" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J816" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K816" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L816" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M816" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N816" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O816" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P816" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q816" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R816" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S816" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T816" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U816" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>Other income (expense)</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>Write-down of goodwill and intangible assets (Notes 6, 7)</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr"/>
+      <c r="E817" s="5" t="n">
+        <v>-0.411146</v>
+      </c>
+      <c r="F817" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G817" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H817" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I817" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J817" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K817" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L817" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M817" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N817" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O817" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P817" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q817" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R817" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S817" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T817" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U817" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>Other income (expense)</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>Write-down of capital assets (Note 5)</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr"/>
+      <c r="E818" s="5" t="n">
+        <v>-0.041318</v>
+      </c>
+      <c r="F818" s="5" t="n">
+        <v>-0.034372</v>
+      </c>
+      <c r="G818" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H818" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I818" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J818" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K818" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L818" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M818" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N818" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O818" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P818" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q818" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R818" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S818" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T818" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U818" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>Other income (expense)</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>Gain on restructuring of accounts payable (Note 10)</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr"/>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F819" s="5" t="n">
+        <v>1.318442</v>
+      </c>
+      <c r="G819" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H819" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I819" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J819" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K819" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L819" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M819" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N819" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O819" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P819" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q819" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R819" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S819" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T819" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U819" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>Other income (expense)</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>Gain on restructuring of preferred shares (Note 11)</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr"/>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F820" s="5" t="n">
+        <v>1.048466</v>
+      </c>
+      <c r="G820" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H820" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I820" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J820" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K820" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L820" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M820" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N820" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O820" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P820" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q820" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R820" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S820" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T820" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U820" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>Other income (expense)</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>Accretion to face value of preferred shares (Note 11)</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr"/>
+      <c r="E821" s="5" t="n">
+        <v>-0.237212</v>
+      </c>
+      <c r="F821" s="5" t="n">
+        <v>-0.309282</v>
+      </c>
+      <c r="G821" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H821" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I821" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J821" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K821" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L821" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M821" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N821" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O821" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P821" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q821" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R821" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S821" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T821" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U821" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>Other income (expense)</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>Dilution loss (Note 14)</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr"/>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F822" s="5" t="n">
+        <v>-0.15188</v>
+      </c>
+      <c r="G822" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H822" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I822" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J822" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K822" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L822" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M822" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N822" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O822" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P822" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q822" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R822" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S822" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T822" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U822" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>Other income (expense)</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>Income (loss) before income taxes</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E823" s="5" t="n">
+        <v>-4.943945</v>
+      </c>
+      <c r="F823" s="5" t="n">
+        <v>1.180604</v>
+      </c>
+      <c r="G823" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H823" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I823" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J823" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K823" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L823" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M823" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N823" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O823" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P823" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q823" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R823" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S823" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T823" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U823" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>Income tax recovery</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr"/>
+      <c r="E824" s="5" t="n">
+        <v>0.369358</v>
+      </c>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H824" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I824" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J824" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K824" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L824" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M824" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N824" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O824" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P824" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q824" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R824" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S824" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T824" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U824" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>Income tax recovery</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>Net income (loss) and comprehensive income (loss) for the year from continuing operations</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr"/>
+      <c r="E825" s="5" t="n">
+        <v>-4.510246</v>
+      </c>
+      <c r="F825" s="5" t="n">
+        <v>1.25114</v>
+      </c>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H825" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I825" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J825" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K825" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L825" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M825" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N825" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O825" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P825" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q825" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R825" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S825" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T825" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U825" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>Income tax recovery</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>Results from discontinued operations (Note 4)</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr"/>
+      <c r="E826" s="5" t="n">
+        <v>4.418501</v>
+      </c>
+      <c r="F826" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G826" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H826" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I826" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J826" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K826" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L826" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M826" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N826" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O826" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P826" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q826" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R826" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S826" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T826" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U826" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>Income tax recovery</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>Net income (loss) and comprehensive income (loss) for the year</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E827" s="5" t="n">
+        <v>-0.09174499999999999</v>
+      </c>
+      <c r="F827" s="5" t="n">
+        <v>1.25114</v>
+      </c>
+      <c r="G827" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H827" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I827" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J827" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K827" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L827" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M827" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N827" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O827" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P827" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q827" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R827" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S827" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T827" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U827" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>Earning per share</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>Basic earnings (loss) per share from continuing operations</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr"/>
+      <c r="E828" s="5" t="n">
+        <v>-1.8e-07</v>
+      </c>
+      <c r="F828" s="5" t="n">
+        <v>5e-08</v>
+      </c>
+      <c r="G828" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H828" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I828" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J828" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K828" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L828" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M828" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N828" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O828" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P828" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q828" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R828" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S828" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T828" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U828" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>Earning per share</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>Basic earnings (loss) per share</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E829" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F829" s="5" t="n">
+        <v>5e-08</v>
+      </c>
+      <c r="G829" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H829" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I829" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J829" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K829" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L829" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M829" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N829" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O829" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P829" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q829" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R829" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S829" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T829" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U829" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>Earning per share</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>Diluted earnings (loss) per share from continuing operations (1)</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr"/>
+      <c r="E830" s="5" t="n">
+        <v>-1.8e-07</v>
+      </c>
+      <c r="F830" s="5" t="n">
+        <v>4e-08</v>
+      </c>
+      <c r="G830" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H830" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I830" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J830" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K830" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L830" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M830" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N830" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O830" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P830" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q830" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R830" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S830" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T830" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U830" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>Earning per share</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>Diluted earnings (loss) per share (1)</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr"/>
+      <c r="E831" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F831" s="5" t="n">
+        <v>4e-08</v>
+      </c>
+      <c r="G831" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H831" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I831" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J831" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K831" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L831" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M831" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N831" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O831" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P831" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q831" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R831" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S831" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T831" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U831" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>Earning per share</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding - basic</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E832" s="5" t="n">
+        <v>24.609495</v>
+      </c>
+      <c r="F832" s="5" t="n">
+        <v>25.891139</v>
+      </c>
+      <c r="G832" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H832" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I832" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J832" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K832" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L832" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M832" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N832" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O832" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P832" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q832" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R832" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S832" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T832" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U832" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>Earning per share</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding - diluted</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>DilutedAverageShares</t>
+        </is>
+      </c>
+      <c r="E833" s="5" t="n">
+        <v>24.609495</v>
+      </c>
+      <c r="F833" s="5" t="n">
+        <v>34.121519</v>
+      </c>
+      <c r="G833" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H833" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I833" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J833" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K833" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L833" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M833" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N833" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O833" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P833" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q833" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R833" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S833" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T833" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U833" t="inlineStr">
         <is>
           <t>-</t>
         </is>
